--- a/data/Sheraton Makkah Availability Chart 17 Sep 2026.xlsx
+++ b/data/Sheraton Makkah Availability Chart 17 Sep 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.10.10\group_data\Sales\Season 2026-2027\Stop Sale\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MGR-TANTAWY\Desktop\STOP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF726835-FF64-4373-9AAC-AC51DEC1285D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DABFC0D-C623-4106-99F0-4FA5FC5D558F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="150" yWindow="0" windowWidth="24945" windowHeight="15600" xr2:uid="{6999B482-4449-4CB2-B7EA-83AD33F735B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6999B482-4449-4CB2-B7EA-83AD33F735B3}"/>
   </bookViews>
   <sheets>
     <sheet name="Stop Sale" sheetId="1" r:id="rId1"/>
@@ -726,6 +726,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="165K Double Only"/>
@@ -1038,6 +1039,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Lock"/>
@@ -1427,6 +1429,9 @@
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Introduction"/>
       <sheetName val="Room Mapping"/>
@@ -1444,6 +1449,9 @@
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Intro"/>
       <sheetName val="Standard Daily (Pd_Mo)"/>
@@ -2254,7 +2262,7 @@
       <c r="V6" s="13"/>
       <c r="W6" s="13"/>
       <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
+      <c r="Y6" s="11"/>
       <c r="Z6" s="13"/>
       <c r="AA6" s="13"/>
       <c r="AB6" s="13"/>
@@ -2290,7 +2298,7 @@
       <c r="V7" s="13"/>
       <c r="W7" s="13"/>
       <c r="X7" s="13"/>
-      <c r="Y7" s="13"/>
+      <c r="Y7" s="11"/>
       <c r="Z7" s="13"/>
       <c r="AA7" s="13"/>
       <c r="AB7" s="13"/>
@@ -2326,7 +2334,7 @@
       <c r="V8" s="13"/>
       <c r="W8" s="13"/>
       <c r="X8" s="13"/>
-      <c r="Y8" s="13"/>
+      <c r="Y8" s="11"/>
       <c r="Z8" s="13"/>
       <c r="AA8" s="13"/>
       <c r="AB8" s="13"/>
@@ -2362,7 +2370,7 @@
       <c r="V9" s="13"/>
       <c r="W9" s="13"/>
       <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
+      <c r="Y9" s="11"/>
       <c r="Z9" s="13"/>
       <c r="AA9" s="13"/>
       <c r="AB9" s="13"/>
